--- a/RunHistory.xlsx
+++ b/RunHistory.xlsx
@@ -204,7 +204,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RunsTable" displayName="RunsTable" ref="A1:I4" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RunsTable" displayName="RunsTable" ref="A1:I8" headerRowCount="1">
   <autoFilter ref="A1:I2"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Run ID"/>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -695,6 +695,166 @@
       </c>
       <c r="I4" s="4" t="n"/>
     </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="2">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26_14-06-40</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIO 3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIOS/SCENARIO 3/DStarLite - Scenario 3.jl</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIOS\SCENARIO 3\Simulation Results\DStarLite_SCENARIO_3_100_123_APM_DF_newAEGL_0.5CM_uncappedTL_2026-09-26_14-06-40.csv</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIOS/SCENARIO 3/Simulation Results/DStarLite_SCENARIO_3_100_123_APM_DF_newAEGL_0.5CM_uncappedTL_2026-09-26_14-06-40.mp4</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIOS\SCENARIO 3\Simulation Results\DStarLite_SCENARIO_3_hist__100_123_APM_DF_newAEGL_0.5CM_uncappedTL_2026-09-26_14-06-40.mp4</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>15.584435</v>
+      </c>
+      <c r="I5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="2">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26_14-16-48</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIO 3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIOS/SCENARIO 3/DStarLite - Scenario 3.jl</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIOS\SCENARIO 3\Simulation Results\DStarLite_SCENARIO_3_100_123_APM_DF_newAEGL_0.5CM_uncappedTL_2026-09-26_14-16-48.csv</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIOS/SCENARIO 3/Simulation Results/DStarLite_SCENARIO_3_100_123_APM_DF_newAEGL_0.5CM_uncappedTL_2026-09-26_14-16-48.mp4</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIOS\SCENARIO 3\Simulation Results\DStarLite_SCENARIO_3_hist__100_123_APM_DF_newAEGL_0.5CM_uncappedTL_2026-09-26_14-16-48.mp4</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>18.734</v>
+      </c>
+      <c r="I6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="2">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26_14-49-41</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIO 3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIOS/SCENARIO 3/DStarLite - Scenario 3.jl</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIOS\SCENARIO 3\Simulation Results\DStarLite_SCENARIO_3_100_123_APM_DF_newAEGL_0.5CM_uncappedTL_2026-09-26_14-49-41.csv</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIOS/SCENARIO 3/Simulation Results/DStarLite_SCENARIO_3_100_123_APM_DF_newAEGL_0.5CM_uncappedTL_2026-09-26_14-49-41.mp4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIOS\SCENARIO 3\Simulation Results\DStarLite_SCENARIO_3_hist__100_123_APM_DF_newAEGL_0.5CM_uncappedTL_2026-09-26_14-49-41.mp4</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>16.227126</v>
+      </c>
+      <c r="I7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="2">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26_15-12-56</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIO 3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIOS/SCENARIO 3/DStarLite - Scenario 3.jl</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIOS\SCENARIO 3\Simulation Results\DStarLite_SCENARIO_3_100_123_APM_DF_newAEGL_0.5CM_uncappedTL_2026-09-26_15-12-56.csv</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIOS/SCENARIO 3/Simulation Results/DStarLite_SCENARIO_3_100_123_APM_DF_newAEGL_0.5CM_uncappedTL_2026-09-26_15-12-56.mp4</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIOS\SCENARIO 3\Simulation Results\DStarLite_SCENARIO_3_hist__100_123_APM_DF_newAEGL_0.5CM_uncappedTL_2026-09-26_15-12-56.mp4</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>14.761939</v>
+      </c>
+      <c r="I8" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
